--- a/artfynd/A 34027-2023 artfynd.xlsx
+++ b/artfynd/A 34027-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124433687</v>
+        <v>124433779</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nya Grossängsbotten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660499</v>
+        <v>660403</v>
       </c>
       <c r="R2" t="n">
-        <v>6694828</v>
+        <v>6694823</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -758,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>&gt;50 korvar i hög på fuktig del av färskt hygge</t>
+          <t>2 korvar på stenhäll</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,11 +785,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Hällmarksbarrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>färskt hygge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124433779</v>
+        <v>124433687</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,43 +814,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nya Grossängsbotten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660403</v>
+        <v>660499</v>
       </c>
       <c r="R3" t="n">
-        <v>6694823</v>
+        <v>6694828</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -890,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>2 korvar på stenhäll</t>
+          <t>&gt;50 korvar i hög på fuktig del av färskt hygge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,6 +915,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>färskt hygge</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 34027-2023 artfynd.xlsx
+++ b/artfynd/A 34027-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124433779</v>
+        <v>124433687</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>56714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nya Grossängsbotten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660403</v>
+        <v>660499</v>
       </c>
       <c r="R2" t="n">
-        <v>6694823</v>
+        <v>6694828</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 korvar på stenhäll</t>
+          <t>&gt;50 korvar i hög på fuktig del av färskt hygge</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +788,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>färskt hygge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124433687</v>
+        <v>124433779</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,46 +822,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nya Grossängsbotten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660499</v>
+        <v>660403</v>
       </c>
       <c r="R3" t="n">
-        <v>6694828</v>
+        <v>6694823</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>&gt;50 korvar i hög på fuktig del av färskt hygge</t>
+          <t>2 korvar på stenhäll</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,11 +920,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Hällmarksbarrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>färskt hygge</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 34027-2023 artfynd.xlsx
+++ b/artfynd/A 34027-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124433779</v>
+        <v>124433687</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>56828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nya Grossängsbotten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660403</v>
+        <v>660499</v>
       </c>
       <c r="R2" t="n">
-        <v>6694823</v>
+        <v>6694828</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 korvar på stenhäll</t>
+          <t>&gt;50 korvar i hög på fuktig del av färskt hygge</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,6 +788,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Hällmarksbarrskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>färskt hygge</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124433687</v>
+        <v>124433779</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,46 +822,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nya Grossängsbotten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660499</v>
+        <v>660403</v>
       </c>
       <c r="R3" t="n">
-        <v>6694828</v>
+        <v>6694823</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +900,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>&gt;50 korvar i hög på fuktig del av färskt hygge</t>
+          <t>2 korvar på stenhäll</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,11 +920,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Hällmarksbarrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>färskt hygge</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
